--- a/Futu_Files/Futu_trades.xlsx
+++ b/Futu_Files/Futu_trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/Futu_Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_0B4E91BF92AC475D6217551030F7C30CE3B0BF56" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D173325E-0CB0-40B5-9C53-1703EC6BBBA5}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0B4E91BF92AC475D621755B6C0204F58E1B8A009" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79C0E6A5-0490-48A0-8794-0B3D7A9152F8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="40">
   <si>
     <t>Account Name</t>
   </si>
@@ -34,6 +34,15 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Exchange</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
     <t>Security</t>
   </si>
   <si>
@@ -43,6 +52,9 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>Ru Dong</t>
   </si>
   <si>
@@ -55,13 +67,25 @@
     <t>Buy</t>
   </si>
   <si>
-    <t>CSOP Hang Seng TECH Index ETF</t>
+    <t>SEHK</t>
+  </si>
+  <si>
+    <t>HK.03033</t>
+  </si>
+  <si>
+    <t>CSOP HKD 1,000 5.0950 5,095.00 -5,112.44 Hang Seng TECH Index ETF</t>
+  </si>
+  <si>
+    <t>HKD</t>
   </si>
   <si>
     <t>06-02-2025</t>
   </si>
   <si>
-    <t>China AMC Select Money Market Fund</t>
+    <t>HK0000502390</t>
+  </si>
+  <si>
+    <t>ChinaAMC Select Money Market Fund</t>
   </si>
   <si>
     <t>10-02-2025</t>
@@ -82,22 +106,34 @@
     <t>19-05-2026</t>
   </si>
   <si>
+    <t>HK.03669</t>
+  </si>
+  <si>
     <t>永達汽車</t>
   </si>
   <si>
-    <t>Yongdaauto</t>
+    <t>Yongdaqiche</t>
+  </si>
+  <si>
+    <t>HK.06618</t>
   </si>
   <si>
     <t>京東健康</t>
   </si>
   <si>
-    <t>Jingdonghealth</t>
+    <t>Jingdongjiankang</t>
+  </si>
+  <si>
+    <t>HK.06993</t>
   </si>
   <si>
     <t>藍月亮集團</t>
   </si>
   <si>
-    <t>Lanyueliang</t>
+    <t>Lanyueliangjituan</t>
+  </si>
+  <si>
+    <t>HK.03690</t>
   </si>
   <si>
     <t>美團-W</t>
@@ -466,13 +502,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="47.7109375" customWidth="1"/>
+    <col min="9" max="9" width="34.42578125" customWidth="1"/>
+    <col min="10" max="10" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,195 +531,279 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3">
+        <v>29.590449</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>924.61605299999997</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>452.42411600000003</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>500</v>
+      </c>
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8">
         <v>1000</v>
       </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>29.590449</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>924.61605299999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>452.42411600000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 INTERNAL</oddFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 CONFIDENTIAL</oddFooter>
   </headerFooter>
 </worksheet>
 </file>